--- a/templates/BNYCL12975 - template.xlsx
+++ b/templates/BNYCL12975 - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
@@ -1349,14 +1349,14 @@
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="25">
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C20" s="27" t="n">
-        <v>1.04168806</v>
+        <v>1.04536086</v>
       </c>
       <c r="D20" s="28" t="n">
-        <v>0.000757758211983095</v>
+        <v>0.0005367055330804948</v>
       </c>
       <c r="E20" s="28" t="n">
         <v>0.0005426623598601132</v>
@@ -1365,23 +1365,23 @@
         <v>0.0006212899469348887</v>
       </c>
       <c r="G20" s="29" t="n">
-        <v>1.396371423620442</v>
+        <v>0.9890229593569859</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>1.219653103549265</v>
+        <v>0.8638567801206377</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="25">
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C21" s="31" t="n">
-        <v>1.04089931</v>
+        <v>1.04480011</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>0.0009767920554488718</v>
+        <v>-0.0008843625997203564</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>0.0005426623598601132</v>
@@ -1390,23 +1390,23 @@
         <v>0.0006212899469348887</v>
       </c>
       <c r="G21" s="33" t="n">
-        <v>1.799999645637239</v>
+        <v>-1.629673743998618</v>
       </c>
       <c r="H21" s="33" t="n">
-        <v>1.572200001412931</v>
+        <v>-1.423429759459858</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="25">
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C22" s="31" t="n">
-        <v>1.03988356</v>
+        <v>1.04572491</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>-0.001209958321779614</v>
+        <v>0.00127881429045229</v>
       </c>
       <c r="E22" s="32" t="n">
         <v>0.0005426623598601132</v>
@@ -1415,23 +1415,23 @@
         <v>0.0006212899469348887</v>
       </c>
       <c r="G22" s="33" t="n">
-        <v>-2.229670622616087</v>
+        <v>2.356556092782889</v>
       </c>
       <c r="H22" s="33" t="n">
-        <v>-1.947493803414813</v>
+        <v>2.058321234330724</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="25">
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C23" s="31" t="n">
-        <v>1.0411433</v>
+        <v>1.04438933</v>
       </c>
       <c r="D23" s="32" t="n">
-        <v>-0.0008551924636961417</v>
+        <v>0.0001519204535158636</v>
       </c>
       <c r="E23" s="32" t="n">
         <v>0.0005426623598601132</v>
@@ -1440,23 +1440,23 @@
         <v>0.0006212899469348887</v>
       </c>
       <c r="G23" s="33" t="n">
-        <v>-1.575919995476731</v>
+        <v>0.2799539174875247</v>
       </c>
       <c r="H23" s="33" t="n">
-        <v>-1.376478837160013</v>
+        <v>0.2445242422887375</v>
       </c>
     </row>
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="25">
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C24" s="31" t="n">
-        <v>1.04203444</v>
+        <v>1.04423069</v>
       </c>
       <c r="D24" s="32" t="n">
-        <v>0.0008864275708702074</v>
+        <v>-0.0004186018947512915</v>
       </c>
       <c r="E24" s="32" t="n">
         <v>0.0005426623598601132</v>
@@ -1465,10 +1465,10 @@
         <v>0.0006212899469348887</v>
       </c>
       <c r="G24" s="33" t="n">
-        <v>1.633479003590206</v>
+        <v>-0.7713855349377799</v>
       </c>
       <c r="H24" s="33" t="n">
-        <v>1.426753442967113</v>
+        <v>-0.6737625432641373</v>
       </c>
     </row>
     <row r="25" ht="15.95" customHeight="1">
@@ -1520,24 +1520,24 @@
     <row r="27" ht="15.95" customFormat="1" customHeight="1" s="25">
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C27" s="34" t="inlineStr"/>
       <c r="D27" s="28" t="n">
-        <v>-0.00386101279607165</v>
+        <v>0.00199557372442638</v>
       </c>
       <c r="E27" s="28" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F27" s="28" t="n">
-        <v>0.01199320179753949</v>
+        <v>0.004357144052575812</v>
       </c>
       <c r="G27" s="29" t="n">
-        <v>-0.3682989086003976</v>
+        <v>0.5244848503451136</v>
       </c>
       <c r="H27" s="29" t="n">
-        <v>-0.3219334470686361</v>
+        <v>0.4580004012597788</v>
       </c>
       <c r="I27" s="35" t="n"/>
     </row>
@@ -1549,19 +1549,19 @@
       </c>
       <c r="C28" s="36" t="inlineStr"/>
       <c r="D28" s="32" t="n">
-        <v>-6.004316138585875e-05</v>
+        <v>-0.0008674924349486579</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>0.01326859116511914</v>
+        <v>0.01318101253458481</v>
       </c>
       <c r="G28" s="33" t="n">
-        <v>-0.005177091889974452</v>
+        <v>-0.0753658312972149</v>
       </c>
       <c r="H28" s="33" t="n">
-        <v>-0.004525209996951446</v>
+        <v>-0.06581379333890323</v>
       </c>
       <c r="I28" s="37" t="n"/>
       <c r="J28" s="38" t="n"/>
@@ -1574,19 +1574,19 @@
       </c>
       <c r="C29" s="36" t="inlineStr"/>
       <c r="D29" s="32" t="n">
-        <v>0.02038828114559355</v>
+        <v>0.01874251379186243</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>0.04042620195026503</v>
+        <v>0.04033627603848444</v>
       </c>
       <c r="G29" s="33" t="n">
-        <v>0.577765856672658</v>
+        <v>0.5324781100020238</v>
       </c>
       <c r="H29" s="33" t="n">
-        <v>0.5043333323935933</v>
+        <v>0.4646565234227468</v>
       </c>
       <c r="I29" s="37" t="n"/>
     </row>
@@ -1598,19 +1598,19 @@
       </c>
       <c r="C30" s="36" t="inlineStr"/>
       <c r="D30" s="32" t="n">
-        <v>0.0177667849932226</v>
+        <v>0.02135524298891367</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>0.03715536110626516</v>
+        <v>0.04361714842343956</v>
       </c>
       <c r="G30" s="33" t="n">
-        <v>0.5476978746915248</v>
+        <v>0.5611621954860918</v>
       </c>
       <c r="H30" s="33" t="n">
-        <v>0.4781755435617809</v>
+        <v>0.4896065827503182</v>
       </c>
       <c r="I30" s="37" t="n"/>
     </row>
@@ -1646,19 +1646,19 @@
       </c>
       <c r="C32" s="36" t="inlineStr"/>
       <c r="D32" s="32" t="n">
-        <v>0.04168806000000003</v>
+        <v>0.04536085999999995</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>0.05312896806104472</v>
+        <v>0.05885787854537639</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>0.06093691176040106</v>
+        <v>0.06754686523296782</v>
       </c>
       <c r="G32" s="33" t="n">
-        <v>0.7846578151508761</v>
+        <v>0.7706845900847253</v>
       </c>
       <c r="H32" s="33" t="n">
-        <v>0.6841183577519331</v>
+        <v>0.6715464861848321</v>
       </c>
       <c r="I32" s="37" t="n"/>
     </row>
@@ -1683,7 +1683,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="46" t="n">
-        <v>19788561.93</v>
+        <v>19776642.6</v>
       </c>
       <c r="I35" s="3" t="n"/>
     </row>
@@ -1696,7 +1696,7 @@
       <c r="C36" s="11" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="46" t="n">
-        <v>25443298.39694737</v>
+        <v>24906321.77542857</v>
       </c>
       <c r="I36" s="3" t="n"/>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D38" s="16" t="n"/>
